--- a/SleepTimes.xlsx
+++ b/SleepTimes.xlsx
@@ -8,17 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UniWork\Creative Coding Dear Data Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F39E8D88-420E-4AC5-BD86-AB119FECFD41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE93BD11-6916-4E54-9A55-39BE5E08BD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EAC68948-DFEA-4671-8075-6E14F60634DA}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Data" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -28,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Time(Digital)</t>
   </si>
@@ -45,28 +56,31 @@
     <t>Difference</t>
   </si>
   <si>
-    <t>Column1</t>
+    <t>Bed2</t>
   </si>
   <si>
-    <t>Column2</t>
+    <t>Sleep3</t>
   </si>
   <si>
-    <t>Column3</t>
-  </si>
-  <si>
-    <t>Column4</t>
+    <t>Date</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
-    <numFmt numFmtId="167" formatCode="hh:mm:ss;@"/>
-    <numFmt numFmtId="168" formatCode="hh:mm"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="166" formatCode="hh:mm"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -75,47 +89,36 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="8">
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -161,12 +164,29 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color theme="4" tint="0.39997558519241921"/>
       </top>
       <bottom style="thin">
         <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
       </bottom>
       <diagonal/>
     </border>
@@ -176,10 +196,10 @@
         <color indexed="64"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color theme="4" tint="0.39997558519241921"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color theme="4" tint="0.39997558519241921"/>
       </bottom>
       <diagonal/>
     </border>
@@ -187,50 +207,72 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color theme="4" tint="0.39997558519241921"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color theme="4" tint="0.39997558519241921"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="20% - Accent1" xfId="1" builtinId="30"/>
+    <cellStyle name="60% - Accent1" xfId="2" builtinId="32"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -239,11 +281,57 @@
         </right>
         <top/>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -251,13 +339,34 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top/>
-        <bottom/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -265,13 +374,33 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top/>
-        <bottom/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -279,27 +408,94 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top/>
-        <bottom/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top/>
-        <bottom/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -319,17 +515,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{31C64684-45F5-4359-9DF6-CE587263A178}" name="Table1" displayName="Table1" ref="A2:F54" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="6">
-  <autoFilter ref="A2:F54" xr:uid="{31C64684-45F5-4359-9DF6-CE587263A178}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0FBAEF08-1BFA-4376-913E-4C9291F5AEEF}" name="Table2" displayName="Table2" ref="A5:F62" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="7">
+  <autoFilter ref="A5:F62" xr:uid="{0FBAEF08-1BFA-4376-913E-4C9291F5AEEF}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{802DB198-370C-47DA-8381-6B69951AF68A}" name="Column1" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{DC1A0FFA-2C03-4716-A2E1-BB757BA5874F}" name="Time(Digital)" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{1ABF9395-5A19-43E5-9A33-CC0F01052D03}" name="Column2" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{B0544AC3-AEF8-4DB6-BA8B-0BCAC916EA0C}" name="Time(Decimal)" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{06E37AB9-003B-42EB-B92D-A0BBA09F86A1}" name="Column3" dataDxfId="1"/>
-    <tableColumn id="6" xr3:uid="{99B63887-E36B-477B-A532-B5AA93204056}" name="Column4"/>
+    <tableColumn id="1" xr3:uid="{F1B5917C-0A21-4668-AE19-CC18AFBA346F}" name="Date" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{EEE8000B-8C5E-4811-B6AB-8CAA9DFB8390}" name="Bed" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{92440288-3AB5-4832-9CBB-24797F85933C}" name="Sleep" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{85B968B3-9D0E-448C-AC51-ADC52D581EFA}" name="Bed2" dataDxfId="3">
+      <calculatedColumnFormula>B6*24</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{815EDEA4-75A9-4C6F-8361-30821BDAC15C}" name="Sleep3" dataDxfId="2">
+      <calculatedColumnFormula>C6*24</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{BC1C5660-F08A-4376-A0CD-AE5BAB6D1994}" name="Difference" dataDxfId="1">
+      <calculatedColumnFormula>MOD(E6-D6,24)</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -649,583 +851,1148 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FB61469-A346-468C-9658-6A61A88D30FC}">
-  <dimension ref="A2:K54"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D61B844D-EE4A-4EFA-8DA9-F91DD3B889C7}">
+  <dimension ref="A4:F62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.77734375" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="6" width="10.44140625" customWidth="1"/>
+    <col min="1" max="1" width="21.5546875" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="14" t="s">
+      <c r="E5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B3" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="10" t="s">
+      <c r="F5" s="17" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="11">
         <v>46308</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B6" s="3">
         <v>0.98124999999999996</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C6" s="3">
         <v>1.0340277777777778</v>
       </c>
-      <c r="D4" s="12">
-        <f>B4*24</f>
+      <c r="D6" s="4">
+        <f>B6*24</f>
         <v>23.549999999999997</v>
       </c>
-      <c r="E4" s="12">
-        <f>C4*24</f>
+      <c r="E6" s="4">
+        <f>C6*24</f>
         <v>24.816666666666666</v>
       </c>
-      <c r="F4" s="8">
-        <f>MOD(E4-D4,24)</f>
+      <c r="F6" s="13">
+        <f>MOD(E6-D6,24)</f>
         <v>1.2666666666666693</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="12">
         <v>46309</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="7"/>
-      <c r="K5" s="1"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="B7" s="5">
+        <v>0.96458333333333335</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.99513888888888891</v>
+      </c>
+      <c r="D7" s="6">
+        <f t="shared" ref="D7:E56" si="0">B7*24</f>
+        <v>23.15</v>
+      </c>
+      <c r="E7" s="6">
+        <f t="shared" si="0"/>
+        <v>23.883333333333333</v>
+      </c>
+      <c r="F7" s="14">
+        <f t="shared" ref="F7:F62" si="1">MOD(E7-D7,24)</f>
+        <v>0.73333333333333428</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="11">
         <v>46310</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="B8" s="3">
+        <v>0.97847222222222219</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1.0062500000000001</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="0"/>
+        <v>23.483333333333334</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" si="0"/>
+        <v>24.150000000000002</v>
+      </c>
+      <c r="F8" s="13">
+        <f t="shared" si="1"/>
+        <v>0.66666666666666785</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="12">
         <v>46311</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E9" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="12">
         <v>46312</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F10" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="12">
         <v>46313</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E11" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="12">
         <v>46314</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="7"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="12">
         <v>46315</v>
       </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+      <c r="B13" s="7"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E13" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="12">
         <v>46316</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F14" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="12">
         <v>46317</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="7"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E15" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="12">
         <v>46318</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="7"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F16" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="12">
         <v>46319</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E17" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F17" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="12">
         <v>46320</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="7"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E18" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F18" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="12">
         <v>46321</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E19" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="12">
         <v>46322</v>
       </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="7"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F20" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="12">
         <v>46323</v>
       </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="7"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E21" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F21" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="12">
         <v>46324</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="3"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E22" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="12">
         <v>46325</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="7"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E23" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="12">
         <v>46326</v>
       </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="7"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E24" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F24" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="12">
         <v>46327</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="7"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E25" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F25" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="12">
         <v>46328</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="7"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E26" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="12">
         <v>46329</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="7"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E27" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="12">
         <v>46330</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="7"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E28" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="12">
         <v>46331</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="7"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E29" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="12">
         <v>46332</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="7"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E30" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="12">
         <v>46333</v>
       </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="7"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="2">
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E31" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="12">
         <v>46334</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="7"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="2">
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E32" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="12">
         <v>46335</v>
       </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="7"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E33" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="12">
         <v>46336</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="7"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E34" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="12">
         <v>46337</v>
       </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="7"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
+      <c r="B35" s="7"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E35" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="12">
         <v>46338</v>
       </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="7"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E36" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="12">
         <v>46339</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="7"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E37" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="12">
         <v>46340</v>
       </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="7"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E38" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="12">
         <v>46341</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="7"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E39" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="12">
         <v>46342</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="7"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="2">
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E40" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="12">
         <v>46343</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="7"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="2">
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E41" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="12">
         <v>46344</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="7"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="2">
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E42" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="12">
         <v>46345</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="7"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="2">
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E43" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="12">
         <v>46346</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="7"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="2">
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E44" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="12">
         <v>46347</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="7"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="2">
+      <c r="B45" s="7"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E45" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="12">
         <v>46348</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="7"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="2">
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E46" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F46" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="12">
         <v>46349</v>
       </c>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="7"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="2">
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E47" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F47" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="12">
         <v>46350</v>
       </c>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="7"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="2">
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E48" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F48" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="12">
         <v>46351</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="7"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="2">
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E49" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F49" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="12">
         <v>46352</v>
       </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="7"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="2">
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E50" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F50" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="12">
         <v>46353</v>
       </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="7"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="2">
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E51" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F51" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="12">
         <v>46354</v>
       </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="3"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="2">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E52" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F52" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="12">
         <v>46355</v>
       </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="7"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="2">
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E53" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F53" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="12">
         <v>46356</v>
       </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="7"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="2">
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E54" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F54" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="12">
         <v>46357</v>
       </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="7"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="2">
+      <c r="B55" s="7"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E55" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F55" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="12">
         <v>46358</v>
       </c>
-      <c r="B54" s="9"/>
-      <c r="C54" s="9"/>
-      <c r="D54" s="10"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="10"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E56" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F56" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="12">
+        <v>46359</v>
+      </c>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="6">
+        <f t="shared" ref="D57:E62" si="2">B57*24</f>
+        <v>0</v>
+      </c>
+      <c r="E57" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F57" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="12">
+        <v>46360</v>
+      </c>
+      <c r="B58" s="10"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E58" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F58" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="12">
+        <v>46361</v>
+      </c>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E59" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F59" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="12">
+        <v>46362</v>
+      </c>
+      <c r="B60" s="10"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E60" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F60" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="12">
+        <v>46363</v>
+      </c>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E61" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F61" s="14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="12">
+        <v>46364</v>
+      </c>
+      <c r="B62" s="10"/>
+      <c r="C62" s="10"/>
+      <c r="D62" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E62" s="4">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F62" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:F4"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/SleepTimes.xlsx
+++ b/SleepTimes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UniWork\Creative Coding Dear Data Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE93BD11-6916-4E54-9A55-39BE5E08BD4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5034D3-BBD7-4ACD-A181-A0BEE68C95DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EAC68948-DFEA-4671-8075-6E14F60634DA}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
-    <numFmt numFmtId="166" formatCode="hh:mm"/>
+    <numFmt numFmtId="165" formatCode="hh:mm"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -89,7 +89,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -111,6 +111,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
@@ -220,28 +226,29 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30"/>
@@ -249,40 +256,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="8">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79998168889431442"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -501,6 +474,40 @@
         </right>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -515,19 +522,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0FBAEF08-1BFA-4376-913E-4C9291F5AEEF}" name="Table2" displayName="Table2" ref="A5:F62" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0FBAEF08-1BFA-4376-913E-4C9291F5AEEF}" name="Table2" displayName="Table2" ref="A5:F62" totalsRowShown="0" headerRowDxfId="7" tableBorderDxfId="6">
   <autoFilter ref="A5:F62" xr:uid="{0FBAEF08-1BFA-4376-913E-4C9291F5AEEF}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F1B5917C-0A21-4668-AE19-CC18AFBA346F}" name="Date" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{EEE8000B-8C5E-4811-B6AB-8CAA9DFB8390}" name="Bed" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{92440288-3AB5-4832-9CBB-24797F85933C}" name="Sleep" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{85B968B3-9D0E-448C-AC51-ADC52D581EFA}" name="Bed2" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{F1B5917C-0A21-4668-AE19-CC18AFBA346F}" name="Date" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{EEE8000B-8C5E-4811-B6AB-8CAA9DFB8390}" name="Bed" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{92440288-3AB5-4832-9CBB-24797F85933C}" name="Sleep" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{85B968B3-9D0E-448C-AC51-ADC52D581EFA}" name="Bed2" dataDxfId="2">
       <calculatedColumnFormula>B6*24</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{815EDEA4-75A9-4C6F-8361-30821BDAC15C}" name="Sleep3" dataDxfId="2">
+    <tableColumn id="5" xr3:uid="{815EDEA4-75A9-4C6F-8361-30821BDAC15C}" name="Sleep3" dataDxfId="1">
       <calculatedColumnFormula>C6*24</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{BC1C5660-F08A-4376-A0CD-AE5BAB6D1994}" name="Difference" dataDxfId="1">
+    <tableColumn id="6" xr3:uid="{BC1C5660-F08A-4376-A0CD-AE5BAB6D1994}" name="Difference" dataDxfId="0">
       <calculatedColumnFormula>MOD(E6-D6,24)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -963,23 +970,27 @@
       <c r="A9" s="12">
         <v>46311</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
+      <c r="B9" s="5">
+        <v>0.9458333333333333</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0.98888888888888893</v>
+      </c>
       <c r="D9" s="6">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22.7</v>
       </c>
       <c r="E9" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23.733333333333334</v>
       </c>
       <c r="F9" s="14">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.033333333333335</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="12">
+      <c r="A10" s="19">
         <v>46312</v>
       </c>
       <c r="B10" s="8"/>
@@ -1017,7 +1028,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="12">
+      <c r="A12" s="19">
         <v>46314</v>
       </c>
       <c r="B12" s="8"/>
@@ -1055,7 +1066,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="12">
+      <c r="A14" s="19">
         <v>46316</v>
       </c>
       <c r="B14" s="8"/>
@@ -1093,7 +1104,7 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="12">
+      <c r="A16" s="19">
         <v>46318</v>
       </c>
       <c r="B16" s="8"/>
@@ -1131,7 +1142,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="12">
+      <c r="A18" s="19">
         <v>46320</v>
       </c>
       <c r="B18" s="8"/>
@@ -1169,7 +1180,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="12">
+      <c r="A20" s="19">
         <v>46322</v>
       </c>
       <c r="B20" s="8"/>
@@ -1207,7 +1218,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="12">
+      <c r="A22" s="19">
         <v>46324</v>
       </c>
       <c r="B22" s="8"/>
@@ -1245,7 +1256,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="12">
+      <c r="A24" s="19">
         <v>46326</v>
       </c>
       <c r="B24" s="8"/>
@@ -1283,7 +1294,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="12">
+      <c r="A26" s="19">
         <v>46328</v>
       </c>
       <c r="B26" s="8"/>
@@ -1321,7 +1332,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="12">
+      <c r="A28" s="19">
         <v>46330</v>
       </c>
       <c r="B28" s="8"/>
@@ -1359,7 +1370,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="12">
+      <c r="A30" s="19">
         <v>46332</v>
       </c>
       <c r="B30" s="8"/>
@@ -1397,7 +1408,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="12">
+      <c r="A32" s="19">
         <v>46334</v>
       </c>
       <c r="B32" s="8"/>
@@ -1435,7 +1446,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="12">
+      <c r="A34" s="19">
         <v>46336</v>
       </c>
       <c r="B34" s="8"/>
@@ -1473,7 +1484,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="12">
+      <c r="A36" s="19">
         <v>46338</v>
       </c>
       <c r="B36" s="8"/>
@@ -1511,7 +1522,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="12">
+      <c r="A38" s="19">
         <v>46340</v>
       </c>
       <c r="B38" s="8"/>
@@ -1549,7 +1560,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="12">
+      <c r="A40" s="19">
         <v>46342</v>
       </c>
       <c r="B40" s="8"/>
@@ -1587,7 +1598,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="12">
+      <c r="A42" s="19">
         <v>46344</v>
       </c>
       <c r="B42" s="8"/>
@@ -1625,7 +1636,7 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="12">
+      <c r="A44" s="19">
         <v>46346</v>
       </c>
       <c r="B44" s="8"/>
@@ -1663,7 +1674,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="12">
+      <c r="A46" s="19">
         <v>46348</v>
       </c>
       <c r="B46" s="8"/>
@@ -1701,7 +1712,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="12">
+      <c r="A48" s="19">
         <v>46350</v>
       </c>
       <c r="B48" s="8"/>
@@ -1739,7 +1750,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="12">
+      <c r="A50" s="19">
         <v>46352</v>
       </c>
       <c r="B50" s="8"/>
@@ -1777,7 +1788,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="12">
+      <c r="A52" s="19">
         <v>46354</v>
       </c>
       <c r="B52" s="8"/>
@@ -1815,7 +1826,7 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="12">
+      <c r="A54" s="19">
         <v>46356</v>
       </c>
       <c r="B54" s="8"/>
@@ -1853,7 +1864,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="12">
+      <c r="A56" s="19">
         <v>46358</v>
       </c>
       <c r="B56" s="10"/>
@@ -1891,7 +1902,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="12">
+      <c r="A58" s="19">
         <v>46360</v>
       </c>
       <c r="B58" s="10"/>
@@ -1929,7 +1940,7 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="12">
+      <c r="A60" s="19">
         <v>46362</v>
       </c>
       <c r="B60" s="10"/>
@@ -1967,7 +1978,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="12">
+      <c r="A62" s="19">
         <v>46364</v>
       </c>
       <c r="B62" s="10"/>

--- a/SleepTimes.xlsx
+++ b/SleepTimes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UniWork\Creative Coding Dear Data Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3459B326-830C-4F64-9061-BB5FCAEC07B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{551CFE13-65B8-4367-8794-1F7AF90FE721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EAC68948-DFEA-4671-8075-6E14F60634DA}"/>
   </bookViews>
@@ -1032,19 +1032,23 @@
       <c r="A12" s="6">
         <v>46313</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
+      <c r="B12" s="13">
+        <v>0.91736111111111107</v>
+      </c>
+      <c r="C12" s="13">
+        <v>1.0333333333333334</v>
+      </c>
       <c r="D12" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22.016666666666666</v>
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24.800000000000004</v>
       </c>
       <c r="F12" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.7833333333333385</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">

--- a/SleepTimes.xlsx
+++ b/SleepTimes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UniWork\Creative Coding Dear Data Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{551CFE13-65B8-4367-8794-1F7AF90FE721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3453E7-7CDD-4EFA-B097-79DDC8B5E388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EAC68948-DFEA-4671-8075-6E14F60634DA}"/>
   </bookViews>
@@ -1055,19 +1055,23 @@
       <c r="A13" s="6">
         <v>46314</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
+      <c r="B13" s="14">
+        <v>0.91249999999999998</v>
+      </c>
+      <c r="C13" s="14">
+        <v>0.95347222222222228</v>
+      </c>
       <c r="D13" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>21.9</v>
       </c>
       <c r="E13" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22.883333333333333</v>
       </c>
       <c r="F13" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.98333333333333428</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">

--- a/SleepTimes.xlsx
+++ b/SleepTimes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UniWork\Creative Coding Dear Data Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3453E7-7CDD-4EFA-B097-79DDC8B5E388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56056D6F-5ECD-4783-8009-01C8F3D66C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EAC68948-DFEA-4671-8075-6E14F60634DA}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Data" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -71,7 +72,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
-    <numFmt numFmtId="168" formatCode="h:mm;@"/>
+    <numFmt numFmtId="165" formatCode="h:mm;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -233,14 +234,14 @@
     <xf numFmtId="2" fontId="1" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30"/>
@@ -860,24 +861,24 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B4" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12" t="s">
+      <c r="B4" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="10" t="s">
@@ -986,10 +987,10 @@
       <c r="A10" s="6">
         <v>46311</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="12">
         <v>1.0034722222222223</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="12">
         <v>1.0402777777777779</v>
       </c>
       <c r="D10" s="3">
@@ -1009,10 +1010,10 @@
       <c r="A11" s="6">
         <v>46312</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="13">
         <v>0.97152777777777777</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="13">
         <v>7.7777777777777779E-2</v>
       </c>
       <c r="D11" s="5">
@@ -1032,10 +1033,10 @@
       <c r="A12" s="6">
         <v>46313</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="12">
         <v>0.91736111111111107</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="12">
         <v>1.0333333333333334</v>
       </c>
       <c r="D12" s="3">
@@ -1055,10 +1056,10 @@
       <c r="A13" s="6">
         <v>46314</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="13">
         <v>0.91249999999999998</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="13">
         <v>0.95347222222222228</v>
       </c>
       <c r="D13" s="5">
@@ -1078,65 +1079,77 @@
       <c r="A14" s="6">
         <v>46315</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
+      <c r="B14" s="12">
+        <v>0.9819444444444444</v>
+      </c>
+      <c r="C14" s="12">
+        <v>1.0368055555555555</v>
+      </c>
       <c r="D14" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23.566666666666666</v>
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24.883333333333333</v>
       </c>
       <c r="F14" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.3166666666666664</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>46316</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
+      <c r="B15" s="13">
+        <v>0.94236111111111109</v>
+      </c>
+      <c r="C15" s="13">
+        <v>0.99027777777777781</v>
+      </c>
       <c r="D15" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22.616666666666667</v>
       </c>
       <c r="E15" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23.766666666666666</v>
       </c>
       <c r="F15" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.1499999999999986</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>46317</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
+      <c r="B16" s="12">
+        <v>0.94236111111111109</v>
+      </c>
+      <c r="C16" s="12">
+        <v>1.0055555555555555</v>
+      </c>
       <c r="D16" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22.616666666666667</v>
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24.133333333333333</v>
       </c>
       <c r="F16" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.5166666666666657</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>46318</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
       <c r="D17" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1154,8 +1167,8 @@
       <c r="A18" s="6">
         <v>46319</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1173,8 +1186,8 @@
       <c r="A19" s="6">
         <v>46320</v>
       </c>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
       <c r="D19" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1192,8 +1205,8 @@
       <c r="A20" s="6">
         <v>46321</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
       <c r="D20" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1211,8 +1224,8 @@
       <c r="A21" s="6">
         <v>46322</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
       <c r="D21" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1230,8 +1243,8 @@
       <c r="A22" s="6">
         <v>46323</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
       <c r="D22" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1249,8 +1262,8 @@
       <c r="A23" s="6">
         <v>46324</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
       <c r="D23" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1268,8 +1281,8 @@
       <c r="A24" s="6">
         <v>46325</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
       <c r="D24" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1287,8 +1300,8 @@
       <c r="A25" s="6">
         <v>46326</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
       <c r="D25" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1306,8 +1319,8 @@
       <c r="A26" s="6">
         <v>46327</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
       <c r="D26" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1325,8 +1338,8 @@
       <c r="A27" s="6">
         <v>46328</v>
       </c>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
       <c r="D27" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1344,8 +1357,8 @@
       <c r="A28" s="6">
         <v>46329</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
       <c r="D28" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1363,8 +1376,8 @@
       <c r="A29" s="6">
         <v>46330</v>
       </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
       <c r="D29" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1382,8 +1395,8 @@
       <c r="A30" s="6">
         <v>46331</v>
       </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
       <c r="D30" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1401,8 +1414,8 @@
       <c r="A31" s="6">
         <v>46332</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
       <c r="D31" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1420,8 +1433,8 @@
       <c r="A32" s="6">
         <v>46333</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
       <c r="D32" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1439,8 +1452,8 @@
       <c r="A33" s="6">
         <v>46334</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
       <c r="D33" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1458,8 +1471,8 @@
       <c r="A34" s="6">
         <v>46335</v>
       </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
       <c r="D34" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1477,8 +1490,8 @@
       <c r="A35" s="6">
         <v>46336</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
       <c r="D35" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1496,8 +1509,8 @@
       <c r="A36" s="6">
         <v>46337</v>
       </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
       <c r="D36" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1515,8 +1528,8 @@
       <c r="A37" s="6">
         <v>46338</v>
       </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
       <c r="D37" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1534,8 +1547,8 @@
       <c r="A38" s="6">
         <v>46339</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
+      <c r="B38" s="12"/>
+      <c r="C38" s="12"/>
       <c r="D38" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1553,8 +1566,8 @@
       <c r="A39" s="6">
         <v>46340</v>
       </c>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
       <c r="D39" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1572,8 +1585,8 @@
       <c r="A40" s="6">
         <v>46341</v>
       </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
       <c r="D40" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1591,8 +1604,8 @@
       <c r="A41" s="6">
         <v>46342</v>
       </c>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
       <c r="D41" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1610,8 +1623,8 @@
       <c r="A42" s="6">
         <v>46343</v>
       </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
       <c r="D42" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1629,8 +1642,8 @@
       <c r="A43" s="6">
         <v>46344</v>
       </c>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
       <c r="D43" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1648,8 +1661,8 @@
       <c r="A44" s="6">
         <v>46345</v>
       </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
       <c r="D44" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1667,8 +1680,8 @@
       <c r="A45" s="6">
         <v>46346</v>
       </c>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
       <c r="D45" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1686,8 +1699,8 @@
       <c r="A46" s="6">
         <v>46347</v>
       </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
+      <c r="B46" s="12"/>
+      <c r="C46" s="12"/>
       <c r="D46" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1705,8 +1718,8 @@
       <c r="A47" s="6">
         <v>46348</v>
       </c>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
       <c r="D47" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1724,8 +1737,8 @@
       <c r="A48" s="6">
         <v>46349</v>
       </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
       <c r="D48" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1743,8 +1756,8 @@
       <c r="A49" s="6">
         <v>46350</v>
       </c>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
       <c r="D49" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1762,8 +1775,8 @@
       <c r="A50" s="6">
         <v>46351</v>
       </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="12"/>
       <c r="D50" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1781,8 +1794,8 @@
       <c r="A51" s="6">
         <v>46352</v>
       </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
       <c r="D51" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1800,8 +1813,8 @@
       <c r="A52" s="6">
         <v>46353</v>
       </c>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
       <c r="D52" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1819,8 +1832,8 @@
       <c r="A53" s="6">
         <v>46354</v>
       </c>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
       <c r="D53" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1838,8 +1851,8 @@
       <c r="A54" s="6">
         <v>46355</v>
       </c>
-      <c r="B54" s="13"/>
-      <c r="C54" s="13"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
       <c r="D54" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1857,8 +1870,8 @@
       <c r="A55" s="6">
         <v>46356</v>
       </c>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
       <c r="D55" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1876,8 +1889,8 @@
       <c r="A56" s="6">
         <v>46357</v>
       </c>
-      <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
+      <c r="B56" s="15"/>
+      <c r="C56" s="15"/>
       <c r="D56" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1895,8 +1908,8 @@
       <c r="A57" s="6">
         <v>46358</v>
       </c>
-      <c r="B57" s="17"/>
-      <c r="C57" s="17"/>
+      <c r="B57" s="16"/>
+      <c r="C57" s="16"/>
       <c r="D57" s="5">
         <f t="shared" ref="D57:E62" si="2">B57*24</f>
         <v>0</v>
@@ -1914,8 +1927,8 @@
       <c r="A58" s="6">
         <v>46359</v>
       </c>
-      <c r="B58" s="16"/>
-      <c r="C58" s="16"/>
+      <c r="B58" s="15"/>
+      <c r="C58" s="15"/>
       <c r="D58" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1933,8 +1946,8 @@
       <c r="A59" s="6">
         <v>46360</v>
       </c>
-      <c r="B59" s="17"/>
-      <c r="C59" s="17"/>
+      <c r="B59" s="16"/>
+      <c r="C59" s="16"/>
       <c r="D59" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1952,8 +1965,8 @@
       <c r="A60" s="6">
         <v>46361</v>
       </c>
-      <c r="B60" s="16"/>
-      <c r="C60" s="16"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="15"/>
       <c r="D60" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1971,8 +1984,8 @@
       <c r="A61" s="6">
         <v>46362</v>
       </c>
-      <c r="B61" s="17"/>
-      <c r="C61" s="17"/>
+      <c r="B61" s="16"/>
+      <c r="C61" s="16"/>
       <c r="D61" s="5">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -1990,8 +2003,8 @@
       <c r="A62" s="6">
         <v>46363</v>
       </c>
-      <c r="B62" s="16"/>
-      <c r="C62" s="16"/>
+      <c r="B62" s="15"/>
+      <c r="C62" s="15"/>
       <c r="D62" s="3">
         <f t="shared" si="2"/>
         <v>0</v>

--- a/SleepTimes.xlsx
+++ b/SleepTimes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UniWork\Creative Coding Dear Data Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56056D6F-5ECD-4783-8009-01C8F3D66C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95416588-7601-445B-8065-718D86604721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EAC68948-DFEA-4671-8075-6E14F60634DA}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Data" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -60,10 +59,10 @@
     <t>Bed2</t>
   </si>
   <si>
-    <t>Sleep3</t>
+    <t>Date</t>
   </si>
   <si>
-    <t>Date</t>
+    <t>Sleep2</t>
   </si>
 </sst>
 </file>
@@ -524,7 +523,7 @@
     <tableColumn id="4" xr3:uid="{85B968B3-9D0E-448C-AC51-ADC52D581EFA}" name="Bed2" dataDxfId="2">
       <calculatedColumnFormula>B6*24</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{815EDEA4-75A9-4C6F-8361-30821BDAC15C}" name="Sleep3" dataDxfId="1">
+    <tableColumn id="5" xr3:uid="{815EDEA4-75A9-4C6F-8361-30821BDAC15C}" name="Sleep2" dataDxfId="1">
       <calculatedColumnFormula>C6*24</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{BC1C5660-F08A-4376-A0CD-AE5BAB6D1994}" name="Difference" dataDxfId="0">
@@ -873,7 +872,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>2</v>
@@ -885,7 +884,7 @@
         <v>5</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>4</v>
@@ -1148,57 +1147,69 @@
       <c r="A17" s="6">
         <v>46318</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
+      <c r="B17" s="13">
+        <v>0.97777777777777775</v>
+      </c>
+      <c r="C17" s="13">
+        <v>1.0229166666666667</v>
+      </c>
       <c r="D17" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23.466666666666665</v>
       </c>
       <c r="E17" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>24.55</v>
       </c>
       <c r="F17" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.0833333333333357</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>46319</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
+      <c r="B18" s="12">
+        <v>0.96805555555555556</v>
+      </c>
+      <c r="C18" s="12">
+        <v>5.7638888888888892E-2</v>
+      </c>
       <c r="D18" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>23.233333333333334</v>
       </c>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.3833333333333333</v>
       </c>
       <c r="F18" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.1499999999999986</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>46320</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
+      <c r="B19" s="13">
+        <v>0.89722222222222225</v>
+      </c>
+      <c r="C19" s="13">
+        <v>0.94652777777777775</v>
+      </c>
       <c r="D19" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>21.533333333333335</v>
       </c>
       <c r="E19" s="5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22.716666666666665</v>
       </c>
       <c r="F19" s="8">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.18333333333333</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">

--- a/SleepTimes.xlsx
+++ b/SleepTimes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UniWork\Creative Coding Dear Data Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95416588-7601-445B-8065-718D86604721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8479FC-7274-4960-8888-F3C5BC0771BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EAC68948-DFEA-4671-8075-6E14F60634DA}"/>
   </bookViews>
@@ -1216,19 +1216,23 @@
       <c r="A20" s="6">
         <v>46321</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
+      <c r="B20" s="12">
+        <v>0.87847222222222221</v>
+      </c>
+      <c r="C20" s="12">
+        <v>0.94027777777777777</v>
+      </c>
       <c r="D20" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>21.083333333333332</v>
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>22.566666666666666</v>
       </c>
       <c r="F20" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.4833333333333343</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
